--- a/main/ig/StructureDefinition-fr-cda-fonctions-physiques.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-fonctions-physiques.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:43:11+00:00</t>
+    <t>2026-09-14T07:43:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-fonctions-physiques.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-fonctions-physiques.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:43:38+00:00</t>
+    <t>2026-10-01T07:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-fonctions-physiques.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-fonctions-physiques.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$102</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$80</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3221" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2549" uniqueCount="304">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T07:35:36+00:00</t>
+    <t>2026-10-14T13:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>IHE-PCC - Physical Function Section. Cette section permet d'enregistrer les problÃ¨mes physiques fonctionnels et structurels qui concernent le patient.</t>
+    <t>IHE-PCC - Physical Function Section. Cette section permet d'enregistrer les problèmes physiques fonctionnels et structurels qui concernent le patient.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -414,7 +414,7 @@
     <t>iheSectionPhysicalFunction</t>
   </si>
   <si>
-    <t>ConformitÃ© Physical Function Section (IHE-PCC)</t>
+    <t>Conformité Physical Function Section (IHE-PCC)</t>
   </si>
   <si>
     <t>Section.templateId:iheSectionPhysicalFunction.nullFlavor</t>
@@ -459,7 +459,7 @@
     <t>frSectionFonctionsPhysiques</t>
   </si>
   <si>
-    <t>ConformitÃ©Â FR-Fonctions-physiques (CI-SIS)</t>
+    <t>Conformité FR-Fonctions-physiques (CI-SIS)</t>
   </si>
   <si>
     <t>Section.templateId:frSectionFonctionsPhysiques.nullFlavor</t>
@@ -593,7 +593,7 @@
     <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
   </si>
   <si>
-    <t>ProblÃ¨mes physiques fonctionnels et structurels</t>
+    <t>Problèmes physiques fonctionnels et structurels</t>
   </si>
   <si>
     <t>CD.displayName</t>
@@ -759,73 +759,36 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>Section.entry:frGroupeDeQuestionnairesDevaluation</t>
-  </si>
-  <si>
-    <t>frGroupeDeQuestionnairesDevaluation</t>
-  </si>
-  <si>
-    <t>Section.entry:frGroupeDeQuestionnairesDevaluation.nullFlavor</t>
+    <t>Entrées Groupe de questionnaires d'évaluation (organizer) et/ou Évaluation (observation)</t>
   </si>
   <si>
     <t>Section.entry.nullFlavor</t>
   </si>
   <si>
-    <t>Section.entry:frGroupeDeQuestionnairesDevaluation.realmCode</t>
-  </si>
-  <si>
     <t>Section.entry.realmCode</t>
   </si>
   <si>
-    <t>Section.entry:frGroupeDeQuestionnairesDevaluation.typeId</t>
-  </si>
-  <si>
     <t>Section.entry.typeId</t>
   </si>
   <si>
-    <t>Section.entry:frGroupeDeQuestionnairesDevaluation.typeId.nullFlavor</t>
-  </si>
-  <si>
     <t>Section.entry.typeId.nullFlavor</t>
   </si>
   <si>
-    <t>Section.entry:frGroupeDeQuestionnairesDevaluation.typeId.assigningAuthorityName</t>
-  </si>
-  <si>
     <t>Section.entry.typeId.assigningAuthorityName</t>
   </si>
   <si>
-    <t>Section.entry:frGroupeDeQuestionnairesDevaluation.typeId.displayable</t>
-  </si>
-  <si>
     <t>Section.entry.typeId.displayable</t>
   </si>
   <si>
-    <t>Section.entry:frGroupeDeQuestionnairesDevaluation.typeId.root</t>
-  </si>
-  <si>
     <t>Section.entry.typeId.root</t>
   </si>
   <si>
-    <t>Section.entry:frGroupeDeQuestionnairesDevaluation.typeId.extension</t>
-  </si>
-  <si>
     <t>Section.entry.typeId.extension</t>
   </si>
   <si>
-    <t>Section.entry:frGroupeDeQuestionnairesDevaluation.templateId</t>
-  </si>
-  <si>
     <t>Section.entry.templateId</t>
   </si>
   <si>
-    <t>Section.entry:frGroupeDeQuestionnairesDevaluation.typeCode</t>
-  </si>
-  <si>
     <t>Section.entry.typeCode</t>
   </si>
   <si>
@@ -838,9 +801,6 @@
     <t>Entry.typeCode</t>
   </si>
   <si>
-    <t>Section.entry:frGroupeDeQuestionnairesDevaluation.contextConductionInd</t>
-  </si>
-  <si>
     <t>Section.entry.contextConductionInd</t>
   </si>
   <si>
@@ -848,9 +808,6 @@
   </si>
   <si>
     <t>Entry.contextConductionInd</t>
-  </si>
-  <si>
-    <t>Section.entry:frGroupeDeQuestionnairesDevaluation.act</t>
   </si>
   <si>
     <t>Section.entry.act</t>
@@ -863,9 +820,6 @@
     <t>Entry.act</t>
   </si>
   <si>
-    <t>Section.entry:frGroupeDeQuestionnairesDevaluation.encounter</t>
-  </si>
-  <si>
     <t>Section.entry.encounter</t>
   </si>
   <si>
@@ -876,20 +830,17 @@
     <t>Entry.encounter</t>
   </si>
   <si>
-    <t>Section.entry:frGroupeDeQuestionnairesDevaluation.observation</t>
-  </si>
-  <si>
     <t>Section.entry.observation</t>
   </si>
   <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Observation
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Observation {https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-evaluation|0.1.0}
 </t>
   </si>
   <si>
+    <t>Entrée Évaluation</t>
+  </si>
+  <si>
     <t>Entry.observation</t>
-  </si>
-  <si>
-    <t>Section.entry:frGroupeDeQuestionnairesDevaluation.observationMedia</t>
   </si>
   <si>
     <t>Section.entry.observationMedia</t>
@@ -902,9 +853,6 @@
     <t>Entry.observationMedia</t>
   </si>
   <si>
-    <t>Section.entry:frGroupeDeQuestionnairesDevaluation.organizer</t>
-  </si>
-  <si>
     <t>Section.entry.organizer</t>
   </si>
   <si>
@@ -912,13 +860,10 @@
 </t>
   </si>
   <si>
-    <t>EntrÃ©e Groupe de questionnaires d'Ã©valutation</t>
+    <t>Entrée Groupe de questionnaires d'évaluation</t>
   </si>
   <si>
     <t>Entry.organizer</t>
-  </si>
-  <si>
-    <t>Section.entry:frGroupeDeQuestionnairesDevaluation.procedure</t>
   </si>
   <si>
     <t>Section.entry.procedure</t>
@@ -931,9 +876,6 @@
     <t>Entry.procedure</t>
   </si>
   <si>
-    <t>Section.entry:frGroupeDeQuestionnairesDevaluation.regionOfInterest</t>
-  </si>
-  <si>
     <t>Section.entry.regionOfInterest</t>
   </si>
   <si>
@@ -944,9 +886,6 @@
     <t>Entry.regionOfInterest</t>
   </si>
   <si>
-    <t>Section.entry:frGroupeDeQuestionnairesDevaluation.substanceAdministration</t>
-  </si>
-  <si>
     <t>Section.entry.substanceAdministration</t>
   </si>
   <si>
@@ -957,9 +896,6 @@
     <t>Entry.substanceAdministration</t>
   </si>
   <si>
-    <t>Section.entry:frGroupeDeQuestionnairesDevaluation.supply</t>
-  </si>
-  <si>
     <t>Section.entry.supply</t>
   </si>
   <si>
@@ -968,83 +904,6 @@
   </si>
   <si>
     <t>Entry.supply</t>
-  </si>
-  <si>
-    <t>Section.entry:frEvaluation</t>
-  </si>
-  <si>
-    <t>frEvaluation</t>
-  </si>
-  <si>
-    <t>Section.entry:frEvaluation.nullFlavor</t>
-  </si>
-  <si>
-    <t>Section.entry:frEvaluation.realmCode</t>
-  </si>
-  <si>
-    <t>Section.entry:frEvaluation.typeId</t>
-  </si>
-  <si>
-    <t>Section.entry:frEvaluation.typeId.nullFlavor</t>
-  </si>
-  <si>
-    <t>Section.entry:frEvaluation.typeId.assigningAuthorityName</t>
-  </si>
-  <si>
-    <t>Section.entry:frEvaluation.typeId.displayable</t>
-  </si>
-  <si>
-    <t>Section.entry:frEvaluation.typeId.root</t>
-  </si>
-  <si>
-    <t>Section.entry:frEvaluation.typeId.extension</t>
-  </si>
-  <si>
-    <t>Section.entry:frEvaluation.templateId</t>
-  </si>
-  <si>
-    <t>Section.entry:frEvaluation.typeCode</t>
-  </si>
-  <si>
-    <t>Section.entry:frEvaluation.contextConductionInd</t>
-  </si>
-  <si>
-    <t>Section.entry:frEvaluation.act</t>
-  </si>
-  <si>
-    <t>Section.entry:frEvaluation.encounter</t>
-  </si>
-  <si>
-    <t>Section.entry:frEvaluation.observation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Observation {https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-evaluation|0.1.0}
-</t>
-  </si>
-  <si>
-    <t>EntrÃ©e Evalutation</t>
-  </si>
-  <si>
-    <t>Section.entry:frEvaluation.observationMedia</t>
-  </si>
-  <si>
-    <t>Section.entry:frEvaluation.organizer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Organizer
-</t>
-  </si>
-  <si>
-    <t>Section.entry:frEvaluation.procedure</t>
-  </si>
-  <si>
-    <t>Section.entry:frEvaluation.regionOfInterest</t>
-  </si>
-  <si>
-    <t>Section.entry:frEvaluation.substanceAdministration</t>
-  </si>
-  <si>
-    <t>Section.entry:frEvaluation.supply</t>
   </si>
   <si>
     <t>Section.component</t>
@@ -1417,12 +1276,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK102"/>
+  <dimension ref="A1:AK80"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="67.765625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="58.69921875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="41.47265625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="31.39453125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="23.3984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="21.37890625" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -6174,7 +6033,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>238</v>
       </c>
@@ -6204,7 +6063,9 @@
       <c r="K47" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="L47" s="2"/>
+      <c r="L47" t="s" s="2">
+        <v>240</v>
+      </c>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6243,14 +6104,16 @@
         <v>75</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="AC47" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>238</v>
@@ -6276,20 +6139,20 @@
         <v>241</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>242</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E48" s="2"/>
+      <c r="E48" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>75</v>
@@ -6301,10 +6164,12 @@
         <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>239</v>
+        <v>86</v>
       </c>
       <c r="L48" s="2"/>
-      <c r="M48" s="2"/>
+      <c r="M48" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6330,13 +6195,11 @@
         <v>75</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>75</v>
@@ -6354,13 +6217,13 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>238</v>
+        <v>90</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>75</v>
@@ -6374,23 +6237,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E49" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>75</v>
@@ -6402,11 +6263,11 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" t="s" s="2">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6433,11 +6294,13 @@
         <v>75</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y49" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z49" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>75</v>
@@ -6455,13 +6318,13 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>75</v>
@@ -6475,10 +6338,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6489,7 +6352,7 @@
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>75</v>
@@ -6501,11 +6364,11 @@
         <v>75</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6556,19 +6419,19 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>75</v>
@@ -6576,16 +6439,18 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E51" s="2"/>
+      <c r="E51" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F51" t="s" s="2">
         <v>81</v>
       </c>
@@ -6602,11 +6467,11 @@
         <v>75</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6633,13 +6498,11 @@
         <v>75</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>75</v>
@@ -6657,7 +6520,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -6669,7 +6532,7 @@
         <v>75</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>75</v>
@@ -6677,17 +6540,17 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>81</v>
@@ -6705,11 +6568,11 @@
         <v>75</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6736,11 +6599,13 @@
         <v>75</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y52" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z52" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>75</v>
@@ -6758,7 +6623,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -6778,17 +6643,17 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F53" t="s" s="2">
         <v>81</v>
@@ -6806,11 +6671,11 @@
         <v>75</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" t="s" s="2">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6861,7 +6726,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -6881,20 +6746,20 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F54" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>76</v>
@@ -6909,11 +6774,11 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" t="s" s="2">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6922,7 +6787,7 @@
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>75</v>
@@ -6964,7 +6829,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -6984,17 +6849,17 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F55" t="s" s="2">
         <v>76</v>
@@ -7012,11 +6877,11 @@
         <v>75</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" t="s" s="2">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7025,7 +6890,7 @@
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>75</v>
@@ -7067,7 +6932,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -7087,23 +6952,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E56" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>75</v>
@@ -7115,11 +6978,11 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7170,13 +7033,13 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>75</v>
@@ -7190,10 +7053,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7204,7 +7067,7 @@
         <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>75</v>
@@ -7216,16 +7079,14 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L57" s="2"/>
-      <c r="M57" t="s" s="2">
-        <v>123</v>
-      </c>
+      <c r="M57" s="2"/>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
-        <v>75</v>
+        <v>251</v>
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
@@ -7247,13 +7108,11 @@
         <v>75</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>75</v>
+        <v>252</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>75</v>
@@ -7271,13 +7130,13 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>126</v>
+        <v>253</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>75</v>
@@ -7291,10 +7150,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7317,18 +7176,18 @@
         <v>75</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
-        <v>263</v>
+        <v>75</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>75</v>
+        <v>255</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>75</v>
@@ -7346,11 +7205,13 @@
         <v>75</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y58" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z58" t="s" s="2">
-        <v>264</v>
+        <v>75</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>75</v>
@@ -7368,7 +7229,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -7388,10 +7249,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7414,7 +7275,7 @@
         <v>75</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>108</v>
+        <v>258</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
@@ -7425,7 +7286,7 @@
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>268</v>
+        <v>75</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>75</v>
@@ -7467,7 +7328,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -7487,10 +7348,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7513,7 +7374,7 @@
         <v>75</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7566,7 +7427,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -7586,10 +7447,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7612,9 +7473,11 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="L61" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="M61" s="2"/>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7665,7 +7528,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -7685,10 +7548,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7711,7 +7574,7 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
@@ -7764,7 +7627,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -7784,10 +7647,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7810,9 +7673,11 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="L63" s="2"/>
+        <v>271</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -7863,7 +7728,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>285</v>
+        <v>273</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -7883,10 +7748,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>286</v>
+        <v>274</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7909,11 +7774,9 @@
         <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="L64" s="2"/>
       <c r="M64" s="2"/>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -7964,7 +7827,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>290</v>
+        <v>276</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -7984,10 +7847,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8010,7 +7873,7 @@
         <v>75</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
@@ -8063,7 +7926,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -8083,10 +7946,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8109,7 +7972,7 @@
         <v>75</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>297</v>
+        <v>281</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -8162,7 +8025,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>298</v>
+        <v>282</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -8182,10 +8045,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8208,7 +8071,7 @@
         <v>75</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>301</v>
+        <v>284</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -8261,7 +8124,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -8281,10 +8144,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8295,7 +8158,7 @@
         <v>81</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>75</v>
@@ -8307,12 +8170,16 @@
         <v>75</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="L68" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+      <c r="O68" t="s" s="2">
+        <v>289</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>75</v>
       </c>
@@ -8360,13 +8227,13 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>75</v>
@@ -8380,23 +8247,23 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="C69" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>290</v>
+      </c>
+      <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E69" s="2"/>
+      <c r="E69" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>75</v>
@@ -8408,10 +8275,12 @@
         <v>75</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>239</v>
+        <v>86</v>
       </c>
       <c r="L69" s="2"/>
-      <c r="M69" s="2"/>
+      <c r="M69" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -8437,13 +8306,11 @@
         <v>75</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>75</v>
@@ -8461,13 +8328,13 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>238</v>
+        <v>90</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>75</v>
@@ -8481,23 +8348,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>309</v>
+        <v>291</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>244</v>
+        <v>291</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E70" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>75</v>
@@ -8509,11 +8374,11 @@
         <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" t="s" s="2">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8540,11 +8405,13 @@
         <v>75</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y70" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z70" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>75</v>
@@ -8562,13 +8429,13 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>75</v>
@@ -8582,10 +8449,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>246</v>
+        <v>292</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8596,7 +8463,7 @@
         <v>81</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>75</v>
@@ -8608,11 +8475,11 @@
         <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8663,19 +8530,19 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>75</v>
@@ -8683,16 +8550,18 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>311</v>
+        <v>293</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>248</v>
+        <v>293</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E72" s="2"/>
+      <c r="E72" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F72" t="s" s="2">
         <v>81</v>
       </c>
@@ -8709,11 +8578,11 @@
         <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" t="s" s="2">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8740,13 +8609,11 @@
         <v>75</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>75</v>
@@ -8764,7 +8631,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -8776,7 +8643,7 @@
         <v>75</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>75</v>
@@ -8784,17 +8651,17 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>312</v>
+        <v>294</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>250</v>
+        <v>294</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="F73" t="s" s="2">
         <v>81</v>
@@ -8812,11 +8679,11 @@
         <v>75</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" t="s" s="2">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -8843,11 +8710,13 @@
         <v>75</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y73" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z73" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>75</v>
@@ -8865,7 +8734,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -8885,17 +8754,17 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>313</v>
+        <v>295</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>252</v>
+        <v>295</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E74" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F74" t="s" s="2">
         <v>81</v>
@@ -8913,11 +8782,11 @@
         <v>75</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" t="s" s="2">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -8968,7 +8837,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -8988,20 +8857,20 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>254</v>
+        <v>296</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F75" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>76</v>
@@ -9016,11 +8885,11 @@
         <v>75</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" t="s" s="2">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9029,7 +8898,7 @@
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>75</v>
@@ -9071,7 +8940,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -9091,17 +8960,17 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>315</v>
+        <v>297</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>256</v>
+        <v>297</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E76" t="s" s="2">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F76" t="s" s="2">
         <v>76</v>
@@ -9119,11 +8988,11 @@
         <v>75</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" t="s" s="2">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -9132,7 +9001,7 @@
       </c>
       <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S76" t="s" s="2">
         <v>75</v>
@@ -9174,7 +9043,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -9194,23 +9063,21 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>316</v>
+        <v>298</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>258</v>
+        <v>298</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E77" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>75</v>
@@ -9222,11 +9089,11 @@
         <v>75</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -9277,13 +9144,13 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>75</v>
@@ -9297,10 +9164,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>317</v>
+        <v>299</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>260</v>
+        <v>299</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9311,7 +9178,7 @@
         <v>81</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>75</v>
@@ -9323,11 +9190,11 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" t="s" s="2">
-        <v>123</v>
+        <v>300</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9336,7 +9203,7 @@
       </c>
       <c r="Q78" s="2"/>
       <c r="R78" t="s" s="2">
-        <v>75</v>
+        <v>251</v>
       </c>
       <c r="S78" t="s" s="2">
         <v>75</v>
@@ -9378,13 +9245,13 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>126</v>
+        <v>299</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>75</v>
@@ -9398,10 +9265,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>318</v>
+        <v>301</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>262</v>
+        <v>301</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9424,18 +9291,18 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
-        <v>263</v>
+        <v>75</v>
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
-        <v>75</v>
+        <v>255</v>
       </c>
       <c r="S79" t="s" s="2">
         <v>75</v>
@@ -9453,11 +9320,13 @@
         <v>75</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y79" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z79" t="s" s="2">
-        <v>264</v>
+        <v>75</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>75</v>
@@ -9475,7 +9344,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>265</v>
+        <v>301</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -9495,10 +9364,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>319</v>
+        <v>302</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>267</v>
+        <v>302</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9506,7 +9375,7 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>76</v>
@@ -9521,7 +9390,7 @@
         <v>75</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>108</v>
+        <v>303</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
@@ -9532,7 +9401,7 @@
       </c>
       <c r="Q80" s="2"/>
       <c r="R80" t="s" s="2">
-        <v>268</v>
+        <v>75</v>
       </c>
       <c r="S80" t="s" s="2">
         <v>75</v>
@@ -9574,10 +9443,10 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>269</v>
+        <v>302</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>76</v>
@@ -9592,2220 +9461,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="81" hidden="true">
-      <c r="A81" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="L81" s="2"/>
-      <c r="M81" s="2"/>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
-      <c r="P81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="82" hidden="true">
-      <c r="A82" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="L82" s="2"/>
-      <c r="M82" s="2"/>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
-      <c r="P82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="83" hidden="true">
-      <c r="A83" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="M83" s="2"/>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
-      <c r="P83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="84" hidden="true">
-      <c r="A84" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E84" s="2"/>
-      <c r="F84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="L84" s="2"/>
-      <c r="M84" s="2"/>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
-      <c r="P84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q84" s="2"/>
-      <c r="R84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="85" hidden="true">
-      <c r="A85" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="C85" s="2"/>
-      <c r="D85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E85" s="2"/>
-      <c r="F85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G85" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K85" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="L85" s="2"/>
-      <c r="M85" s="2"/>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
-      <c r="P85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q85" s="2"/>
-      <c r="R85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>290</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH85" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK85" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="86" hidden="true">
-      <c r="A86" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="C86" s="2"/>
-      <c r="D86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E86" s="2"/>
-      <c r="F86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G86" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K86" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="L86" s="2"/>
-      <c r="M86" s="2"/>
-      <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
-      <c r="P86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q86" s="2"/>
-      <c r="R86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AG86" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH86" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK86" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="87" hidden="true">
-      <c r="A87" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="C87" s="2"/>
-      <c r="D87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E87" s="2"/>
-      <c r="F87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="L87" s="2"/>
-      <c r="M87" s="2"/>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
-      <c r="P87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q87" s="2"/>
-      <c r="R87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="AG87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH87" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ87" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK87" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="88" hidden="true">
-      <c r="A88" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="D88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E88" s="2"/>
-      <c r="F88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G88" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K88" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="L88" s="2"/>
-      <c r="M88" s="2"/>
-      <c r="N88" s="2"/>
-      <c r="O88" s="2"/>
-      <c r="P88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q88" s="2"/>
-      <c r="R88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="AG88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH88" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ88" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="89" hidden="true">
-      <c r="A89" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="B89" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="C89" s="2"/>
-      <c r="D89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E89" s="2"/>
-      <c r="F89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G89" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K89" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="L89" s="2"/>
-      <c r="M89" s="2"/>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
-      <c r="P89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q89" s="2"/>
-      <c r="R89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF89" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AG89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK89" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="90" hidden="true">
-      <c r="A90" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="B90" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="C90" s="2"/>
-      <c r="D90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E90" s="2"/>
-      <c r="F90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K90" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="M90" s="2"/>
-      <c r="N90" s="2"/>
-      <c r="O90" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="P90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q90" s="2"/>
-      <c r="R90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF90" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="AG90" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH90" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ90" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK90" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="91" hidden="true">
-      <c r="A91" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="B91" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="C91" s="2"/>
-      <c r="D91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="F91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G91" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K91" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L91" s="2"/>
-      <c r="M91" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
-      <c r="P91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q91" s="2"/>
-      <c r="R91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X91" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y91" s="2"/>
-      <c r="Z91" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AG91" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH91" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ91" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK91" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="92" hidden="true">
-      <c r="A92" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="C92" s="2"/>
-      <c r="D92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E92" s="2"/>
-      <c r="F92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K92" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L92" s="2"/>
-      <c r="M92" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
-      <c r="P92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q92" s="2"/>
-      <c r="R92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF92" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AG92" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK92" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="93" hidden="true">
-      <c r="A93" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="B93" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="C93" s="2"/>
-      <c r="D93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E93" s="2"/>
-      <c r="F93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G93" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K93" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L93" s="2"/>
-      <c r="M93" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="N93" s="2"/>
-      <c r="O93" s="2"/>
-      <c r="P93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q93" s="2"/>
-      <c r="R93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AG93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH93" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ93" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK93" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="94" hidden="true">
-      <c r="A94" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="C94" s="2"/>
-      <c r="D94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E94" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="F94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G94" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K94" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L94" s="2"/>
-      <c r="M94" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
-      <c r="P94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q94" s="2"/>
-      <c r="R94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y94" s="2"/>
-      <c r="Z94" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AG94" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH94" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ94" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK94" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="95" hidden="true">
-      <c r="A95" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="C95" s="2"/>
-      <c r="D95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E95" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="F95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G95" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K95" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L95" s="2"/>
-      <c r="M95" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N95" s="2"/>
-      <c r="O95" s="2"/>
-      <c r="P95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q95" s="2"/>
-      <c r="R95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AG95" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH95" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK95" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="96" hidden="true">
-      <c r="A96" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="C96" s="2"/>
-      <c r="D96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E96" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="F96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G96" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K96" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L96" s="2"/>
-      <c r="M96" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
-      <c r="P96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q96" s="2"/>
-      <c r="R96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="97" hidden="true">
-      <c r="A97" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E97" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="F97" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G97" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K97" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="L97" s="2"/>
-      <c r="M97" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N97" s="2"/>
-      <c r="O97" s="2"/>
-      <c r="P97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q97" s="2"/>
-      <c r="R97" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="S97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="98" hidden="true">
-      <c r="A98" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E98" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="F98" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K98" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L98" s="2"/>
-      <c r="M98" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
-      <c r="P98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q98" s="2"/>
-      <c r="R98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="99" hidden="true">
-      <c r="A99" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="D99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K99" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L99" s="2"/>
-      <c r="M99" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="N99" s="2"/>
-      <c r="O99" s="2"/>
-      <c r="P99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q99" s="2"/>
-      <c r="R99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="100" hidden="true">
-      <c r="A100" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="C100" s="2"/>
-      <c r="D100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E100" s="2"/>
-      <c r="F100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G100" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K100" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L100" s="2"/>
-      <c r="M100" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
-      <c r="P100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q100" s="2"/>
-      <c r="R100" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="S100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK100" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="101" hidden="true">
-      <c r="A101" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="C101" s="2"/>
-      <c r="D101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E101" s="2"/>
-      <c r="F101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G101" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K101" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L101" s="2"/>
-      <c r="M101" s="2"/>
-      <c r="N101" s="2"/>
-      <c r="O101" s="2"/>
-      <c r="P101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q101" s="2"/>
-      <c r="R101" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="S101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="AG101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ101" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK101" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="102" hidden="true">
-      <c r="A102" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="C102" s="2"/>
-      <c r="D102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E102" s="2"/>
-      <c r="F102" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G102" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K102" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="L102" s="2"/>
-      <c r="M102" s="2"/>
-      <c r="N102" s="2"/>
-      <c r="O102" s="2"/>
-      <c r="P102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q102" s="2"/>
-      <c r="R102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="AG102" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH102" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ102" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK102" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AK102">
+  <autoFilter ref="A1:AK80">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -11815,7 +9472,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI101">
+  <conditionalFormatting sqref="A2:AI79">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-cda-fonctions-physiques.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-fonctions-physiques.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T13:15:36+00:00</t>
+    <t>2026-10-15T09:41:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-fonctions-physiques.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-fonctions-physiques.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T09:41:25+00:00</t>
+    <t>2026-10-15T10:11:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-fonctions-physiques.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-fonctions-physiques.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:11:14+00:00</t>
+    <t>2026-10-15T11:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-fonctions-physiques.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-fonctions-physiques.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:51:04+00:00</t>
+    <t>2026-10-15T13:36:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-fonctions-physiques.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-fonctions-physiques.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:36:09+00:00</t>
+    <t>2026-10-15T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-fonctions-physiques.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-fonctions-physiques.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T15:46:20+00:00</t>
+    <t>2026-10-16T07:40:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-fonctions-physiques.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-fonctions-physiques.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T07:40:35+00:00</t>
+    <t>2026-10-16T08:34:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-fonctions-physiques.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-fonctions-physiques.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T08:34:24+00:00</t>
+    <t>2026-10-16T09:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-fonctions-physiques.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-fonctions-physiques.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:04:08+00:00</t>
+    <t>2026-10-16T11:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
